--- a/research/traditional_assets/database/data/lebanon/lebanon_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/lebanon/lebanon_bank_money_center.xlsx
@@ -587,26 +587,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.158</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
       <c r="K2">
-        <v>-94.3</v>
-      </c>
-      <c r="L2">
-        <v>-0.5297752808988764</v>
+        <v>-899</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,55 +612,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7718.9</v>
+        <v>11463.3</v>
       </c>
       <c r="V2">
-        <v>16.74018651051832</v>
+        <v>12.67363184079602</v>
       </c>
       <c r="W2">
-        <v>-0.07582214360376296</v>
+        <v>-0.4411403896167623</v>
       </c>
       <c r="X2">
-        <v>0.5723652806704527</v>
+        <v>0.5904020739026912</v>
       </c>
       <c r="Y2">
-        <v>-0.6481874242742156</v>
+        <v>-1.031542463519453</v>
       </c>
       <c r="Z2">
-        <v>-0.0443713231628278</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.2609269713314231</v>
+        <v>0.2759995303671481</v>
       </c>
       <c r="AC2">
-        <v>-0.2609269713314231</v>
+        <v>-0.2759995303671481</v>
       </c>
       <c r="AD2">
-        <v>1596.7</v>
+        <v>3341.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1596.7</v>
+        <v>3341.7</v>
       </c>
       <c r="AG2">
-        <v>-6122.2</v>
+        <v>-8121.599999999999</v>
       </c>
       <c r="AH2">
-        <v>0.7759257459422684</v>
+        <v>0.7869860110216194</v>
       </c>
       <c r="AI2">
-        <v>0.5061497495720535</v>
+        <v>0.6753910829055338</v>
       </c>
       <c r="AJ2">
-        <v>1.081450601473212</v>
+        <v>1.12532734754957</v>
       </c>
       <c r="AK2">
-        <v>1.341322875358763</v>
+        <v>1.246504489294759</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -695,7 +677,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Byblos Bank S.A.L. (BDB:BYB)</t>
+          <t>Bank Audi sal (BDB:AUDI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -703,26 +685,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.158</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>-94.3</v>
-      </c>
-      <c r="L3">
-        <v>-0.5297752808988764</v>
+        <v>-899</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,55 +710,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7718.9</v>
+        <v>11463.3</v>
       </c>
       <c r="V3">
-        <v>16.74018651051832</v>
+        <v>12.67363184079602</v>
       </c>
       <c r="W3">
-        <v>-0.07582214360376296</v>
+        <v>-0.4411403896167623</v>
       </c>
       <c r="X3">
-        <v>0.5723652806704527</v>
+        <v>0.5904020739026912</v>
       </c>
       <c r="Y3">
-        <v>-0.6481874242742156</v>
+        <v>-1.031542463519453</v>
       </c>
       <c r="Z3">
-        <v>-0.0443713231628278</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.2609269713314231</v>
+        <v>0.2759995303671481</v>
       </c>
       <c r="AC3">
-        <v>-0.2609269713314231</v>
+        <v>-0.2759995303671481</v>
       </c>
       <c r="AD3">
-        <v>1596.7</v>
+        <v>3341.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1596.7</v>
+        <v>3341.7</v>
       </c>
       <c r="AG3">
-        <v>-6122.2</v>
+        <v>-8121.599999999999</v>
       </c>
       <c r="AH3">
-        <v>0.7759257459422684</v>
+        <v>0.7869860110216194</v>
       </c>
       <c r="AI3">
-        <v>0.5061497495720535</v>
+        <v>0.6753910829055338</v>
       </c>
       <c r="AJ3">
-        <v>1.081450601473212</v>
+        <v>1.12532734754957</v>
       </c>
       <c r="AK3">
-        <v>1.341322875358763</v>
+        <v>1.246504489294759</v>
       </c>
       <c r="AL3">
         <v>0</v>
